--- a/БД/funcs/DZT2_LVALH.xlsx
+++ b/БД/funcs/DZT2_LVALH.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="28290" windowHeight="12585" activeTab="2"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="28290" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="Controls" sheetId="4" r:id="rId1"/>
@@ -827,7 +827,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -861,6 +861,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -926,7 +932,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1087,14 +1093,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1499,15 +1508,15 @@
       <c r="AW1" s="11"/>
       <c r="AX1" s="11"/>
       <c r="AY1" s="13"/>
-      <c r="AZ1" s="58" t="s">
+      <c r="AZ1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="BA1" s="59"/>
-      <c r="BB1" s="59"/>
-      <c r="BC1" s="59"/>
-      <c r="BD1" s="59"/>
-      <c r="BE1" s="59"/>
-      <c r="BF1" s="59"/>
+      <c r="BA1" s="60"/>
+      <c r="BB1" s="60"/>
+      <c r="BC1" s="60"/>
+      <c r="BD1" s="60"/>
+      <c r="BE1" s="60"/>
+      <c r="BF1" s="60"/>
     </row>
     <row r="2" spans="1:16379" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -18098,22 +18107,20 @@
       <c r="AS3" s="31">
         <v>0</v>
       </c>
-      <c r="AT3" s="31">
-        <v>0</v>
+      <c r="AT3" s="61">
+        <v>1</v>
       </c>
       <c r="AU3" s="31">
         <v>0</v>
       </c>
-      <c r="AV3" s="31">
-        <f t="shared" ref="AV3" si="2">BIN2DEC(CONCATENATE(0,0,0,0,AR3,AS3,AT3,AU3))</f>
-        <v>0</v>
-      </c>
-      <c r="AW3" s="31">
-        <v>0</v>
-      </c>
-      <c r="AX3" s="31">
-        <f t="shared" ref="AX3:AX37" si="3">BIN2DEC(CONCATENATE(0,0,0,0,AT3,AU3,AV3,AW3))</f>
-        <v>0</v>
+      <c r="AV3" s="61">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="61">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="61">
+        <v>1</v>
       </c>
       <c r="AY3" s="31"/>
       <c r="AZ3" s="28"/>
@@ -18124,7 +18131,7 @@
       <c r="BE3" s="35"/>
       <c r="BF3" s="31"/>
       <c r="BG3" s="36" t="str">
-        <f t="shared" ref="BG3" si="4">CONCATENATE("description: """,F3,"""", ", ", "note: """,E3,"""",", ","group: """, B3, """",", ","minValue: ", S3,", ","maxValue: ", T3,", ","step: ", U3,", ","units: """, R3, """",", ","defaultValue: ", X3,", ","eventRegistration: ", Y3,)</f>
+        <f t="shared" ref="BG3" si="2">CONCATENATE("description: """,F3,"""", ", ", "note: """,E3,"""",", ","group: """, B3, """",", ","minValue: ", S3,", ","maxValue: ", T3,", ","step: ", U3,", ","units: """, R3, """",", ","defaultValue: ", X3,", ","eventRegistration: ", Y3,)</f>
         <v>description: "Вывод терминала", note: "Вывод терминала", group: "control", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH3" s="37"/>
@@ -18147,7 +18154,7 @@
       </c>
       <c r="H4" s="25"/>
       <c r="I4" s="25">
-        <f t="shared" ref="I4:I6" si="5">LEN(F4)</f>
+        <f t="shared" ref="I4:I6" si="3">LEN(F4)</f>
         <v>13</v>
       </c>
       <c r="J4" s="25" t="str">
@@ -18228,14 +18235,14 @@
         <v>0</v>
       </c>
       <c r="AV4" s="31">
-        <f t="shared" ref="AV4:AV6" si="6">BIN2DEC(CONCATENATE(0,0,0,0,AR4,AS4,AT4,AU4))</f>
+        <f t="shared" ref="AV4:AV6" si="4">BIN2DEC(CONCATENATE(0,0,0,0,AR4,AS4,AT4,AU4))</f>
         <v>0</v>
       </c>
       <c r="AW4" s="31">
         <v>0</v>
       </c>
       <c r="AX4" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="AX3:AX37" si="5">BIN2DEC(CONCATENATE(0,0,0,0,AT4,AU4,AV4,AW4))</f>
         <v>0</v>
       </c>
       <c r="AY4" s="31"/>
@@ -18247,7 +18254,7 @@
       <c r="BE4" s="35"/>
       <c r="BF4" s="31"/>
       <c r="BG4" s="36" t="str">
-        <f t="shared" ref="BG4:BG6" si="7">CONCATENATE("description: """,F4,"""", ", ", "note: """,E4,"""",", ","group: """, B4, """",", ","minValue: ", S4,", ","maxValue: ", T4,", ","step: ", U4,", ","units: """, R4, """",", ","defaultValue: ", X4,", ","eventRegistration: ", Y4,)</f>
+        <f t="shared" ref="BG4:BG6" si="6">CONCATENATE("description: """,F4,"""", ", ", "note: """,E4,"""",", ","group: """, B4, """",", ","minValue: ", S4,", ","maxValue: ", T4,", ","step: ", U4,", ","units: """, R4, """",", ","defaultValue: ", X4,", ","eventRegistration: ", Y4,)</f>
         <v>description: "Сраб.сигн ДТО", note: "Срабатывание ДТО на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH4" s="37"/>
@@ -18270,7 +18277,7 @@
       </c>
       <c r="H5" s="25"/>
       <c r="I5" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="J5" s="25" t="str">
@@ -18351,14 +18358,14 @@
         <v>0</v>
       </c>
       <c r="AV5" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AW5" s="31">
         <v>0</v>
       </c>
       <c r="AX5" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY5" s="31"/>
@@ -18370,7 +18377,7 @@
       <c r="BE5" s="35"/>
       <c r="BF5" s="31"/>
       <c r="BG5" s="36" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>description: "Сраб.сигн ДТЗт", note: "Срабатывание ДТЗт на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH5" s="37"/>
@@ -18393,7 +18400,7 @@
       </c>
       <c r="H6" s="25"/>
       <c r="I6" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="J6" s="25" t="str">
@@ -18474,14 +18481,14 @@
         <v>0</v>
       </c>
       <c r="AV6" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AW6" s="31">
         <v>0</v>
       </c>
       <c r="AX6" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY6" s="31"/>
@@ -18493,7 +18500,7 @@
       <c r="BE6" s="35"/>
       <c r="BF6" s="31"/>
       <c r="BG6" s="36" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>description: "Сраб. КЦТнеб", note: "Срабатывание КЦТнеб", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH6" s="37"/>
@@ -18516,7 +18523,7 @@
       </c>
       <c r="H7" s="25"/>
       <c r="I7" s="25">
-        <f t="shared" ref="I7:I8" si="8">LEN(F7)</f>
+        <f t="shared" ref="I7:I8" si="7">LEN(F7)</f>
         <v>9</v>
       </c>
       <c r="J7" s="25" t="str">
@@ -18597,14 +18604,14 @@
         <v>0</v>
       </c>
       <c r="AV7" s="31">
-        <f t="shared" ref="AV7:AV8" si="9">BIN2DEC(CONCATENATE(0,0,0,0,AR7,AS7,AT7,AU7))</f>
+        <f t="shared" ref="AV7:AV8" si="8">BIN2DEC(CONCATENATE(0,0,0,0,AR7,AS7,AT7,AU7))</f>
         <v>0</v>
       </c>
       <c r="AW7" s="31">
         <v>0</v>
       </c>
       <c r="AX7" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY7" s="31"/>
@@ -18616,7 +18623,7 @@
       <c r="BE7" s="35"/>
       <c r="BF7" s="31"/>
       <c r="BG7" s="36" t="str">
-        <f t="shared" ref="BG7:BG8" si="10">CONCATENATE("description: """,F7,"""", ", ", "note: """,E7,"""",", ","group: """, B7, """",", ","minValue: ", S7,", ","maxValue: ", T7,", ","step: ", U7,", ","units: """, R7, """",", ","defaultValue: ", X7,", ","eventRegistration: ", Y7,)</f>
+        <f t="shared" ref="BG7:BG8" si="9">CONCATENATE("description: """,F7,"""", ", ", "note: """,E7,"""",", ","group: """, B7, """",", ","minValue: ", S7,", ","maxValue: ", T7,", ","step: ", U7,", ","units: """, R7, """",", ","defaultValue: ", X7,", ","eventRegistration: ", Y7,)</f>
         <v>description: "Сраб. КЦТ", note: "Срабатывание КЦТ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH7" s="37"/>
@@ -18639,7 +18646,7 @@
       </c>
       <c r="H8" s="25"/>
       <c r="I8" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="J8" s="25" t="str">
@@ -18720,14 +18727,14 @@
         <v>0</v>
       </c>
       <c r="AV8" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AW8" s="31">
         <v>0</v>
       </c>
       <c r="AX8" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY8" s="31"/>
@@ -18739,7 +18746,7 @@
       <c r="BE8" s="35"/>
       <c r="BF8" s="31"/>
       <c r="BG8" s="36" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>description: "Сраб.сигн ЛО ГЗсигн", note: "Срабатывание ЛО ГЗсигн на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH8" s="37"/>
@@ -18762,11 +18769,11 @@
       </c>
       <c r="H9" s="25"/>
       <c r="I9" s="25">
-        <f t="shared" ref="I9:I33" si="11">LEN(F9)</f>
+        <f t="shared" ref="I9:I33" si="10">LEN(F9)</f>
         <v>19</v>
       </c>
       <c r="J9" s="25" t="str">
-        <f t="shared" ref="J9:J33" si="12">IF(LEN(F9)&lt;=$J$1,F9,"")</f>
+        <f t="shared" ref="J9:J33" si="11">IF(LEN(F9)&lt;=$J$1,F9,"")</f>
         <v>Сраб.сигн ЛО ГЗоткл</v>
       </c>
       <c r="K9" s="23" t="s">
@@ -18843,14 +18850,14 @@
         <v>0</v>
       </c>
       <c r="AV9" s="31">
-        <f t="shared" ref="AV9:AV33" si="13">BIN2DEC(CONCATENATE(0,0,0,0,AR9,AS9,AT9,AU9))</f>
+        <f t="shared" ref="AV9:AV33" si="12">BIN2DEC(CONCATENATE(0,0,0,0,AR9,AS9,AT9,AU9))</f>
         <v>0</v>
       </c>
       <c r="AW9" s="31">
         <v>0</v>
       </c>
       <c r="AX9" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY9" s="31"/>
@@ -18862,7 +18869,7 @@
       <c r="BE9" s="35"/>
       <c r="BF9" s="31"/>
       <c r="BG9" s="36" t="str">
-        <f t="shared" ref="BG9:BG33" si="14">CONCATENATE("description: """,F9,"""", ", ", "note: """,E9,"""",", ","group: """, B9, """",", ","minValue: ", S9,", ","maxValue: ", T9,", ","step: ", U9,", ","units: """, R9, """",", ","defaultValue: ", X9,", ","eventRegistration: ", Y9,)</f>
+        <f t="shared" ref="BG9:BG33" si="13">CONCATENATE("description: """,F9,"""", ", ", "note: """,E9,"""",", ","group: """, B9, """",", ","minValue: ", S9,", ","maxValue: ", T9,", ","step: ", U9,", ","units: """, R9, """",", ","defaultValue: ", X9,", ","eventRegistration: ", Y9,)</f>
         <v>description: "Сраб.сигн ЛО ГЗоткл", note: "Срабатывание ЛО ГЗоткл на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH9" s="37"/>
@@ -18885,11 +18892,11 @@
       </c>
       <c r="H10" s="25"/>
       <c r="I10" s="25">
+        <f t="shared" si="10"/>
+        <v>19</v>
+      </c>
+      <c r="J10" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>19</v>
-      </c>
-      <c r="J10" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ГЗ РПН</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -18966,14 +18973,14 @@
         <v>0</v>
       </c>
       <c r="AV10" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW10" s="31">
         <v>0</v>
       </c>
       <c r="AX10" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY10" s="31"/>
@@ -18985,7 +18992,7 @@
       <c r="BE10" s="35"/>
       <c r="BF10" s="31"/>
       <c r="BG10" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ГЗ РПН", note: "Срабатывание ЛО ГЗ РПН на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH10" s="37"/>
@@ -19008,11 +19015,11 @@
       </c>
       <c r="H11" s="25"/>
       <c r="I11" s="25">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="J11" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="J11" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ДТм</v>
       </c>
       <c r="K11" s="23" t="s">
@@ -19089,14 +19096,14 @@
         <v>0</v>
       </c>
       <c r="AV11" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW11" s="31">
         <v>0</v>
       </c>
       <c r="AX11" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY11" s="31"/>
@@ -19108,7 +19115,7 @@
       <c r="BE11" s="35"/>
       <c r="BF11" s="31"/>
       <c r="BG11" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ДТм", note: "Срабатывание ЛО ДТм", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH11" s="37"/>
@@ -19131,11 +19138,11 @@
       </c>
       <c r="H12" s="25"/>
       <c r="I12" s="25">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="J12" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="J12" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ДТо</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -19212,14 +19219,14 @@
         <v>0</v>
       </c>
       <c r="AV12" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW12" s="31">
         <v>0</v>
       </c>
       <c r="AX12" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY12" s="31"/>
@@ -19231,7 +19238,7 @@
       <c r="BE12" s="35"/>
       <c r="BF12" s="31"/>
       <c r="BG12" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ДТо", note: "Срабатывание ЛО ДТо", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH12" s="37"/>
@@ -19254,11 +19261,11 @@
       </c>
       <c r="H13" s="25"/>
       <c r="I13" s="25">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="J13" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="J13" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО РД</v>
       </c>
       <c r="K13" s="23" t="s">
@@ -19335,14 +19342,14 @@
         <v>0</v>
       </c>
       <c r="AV13" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW13" s="31">
         <v>0</v>
       </c>
       <c r="AX13" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY13" s="31"/>
@@ -19354,7 +19361,7 @@
       <c r="BE13" s="35"/>
       <c r="BF13" s="31"/>
       <c r="BG13" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО РД", note: "Срабатывание ЛО РД на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH13" s="37"/>
@@ -19377,11 +19384,11 @@
       </c>
       <c r="H14" s="25"/>
       <c r="I14" s="25">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="J14" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="J14" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ПК</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -19458,14 +19465,14 @@
         <v>0</v>
       </c>
       <c r="AV14" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW14" s="31">
         <v>0</v>
       </c>
       <c r="AX14" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY14" s="31"/>
@@ -19477,7 +19484,7 @@
       <c r="BE14" s="35"/>
       <c r="BF14" s="31"/>
       <c r="BG14" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ПК", note: "Срабатывание ЛО ПК на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH14" s="37"/>
@@ -19500,11 +19507,11 @@
       </c>
       <c r="H15" s="25"/>
       <c r="I15" s="25">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="J15" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="J15" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ОК</v>
       </c>
       <c r="K15" s="23" t="s">
@@ -19581,14 +19588,14 @@
         <v>0</v>
       </c>
       <c r="AV15" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW15" s="31">
         <v>0</v>
       </c>
       <c r="AX15" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY15" s="31"/>
@@ -19600,7 +19607,7 @@
       <c r="BE15" s="35"/>
       <c r="BF15" s="31"/>
       <c r="BG15" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ОК", note: "Срабатывание ЛО ОК на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH15" s="37"/>
@@ -19623,11 +19630,11 @@
       </c>
       <c r="H16" s="25"/>
       <c r="I16" s="25">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="J16" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>18</v>
-      </c>
-      <c r="J16" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ДУм Р</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -19704,14 +19711,14 @@
         <v>0</v>
       </c>
       <c r="AV16" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW16" s="31">
         <v>0</v>
       </c>
       <c r="AX16" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY16" s="31"/>
@@ -19723,7 +19730,7 @@
       <c r="BE16" s="35"/>
       <c r="BF16" s="31"/>
       <c r="BG16" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ДУм Р", note: "Срабатывание ЛО ДУм расширителя на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH16" s="37"/>
@@ -19746,11 +19753,11 @@
       </c>
       <c r="H17" s="25"/>
       <c r="I17" s="25">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="J17" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>13</v>
-      </c>
-      <c r="J17" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЗПО</v>
       </c>
       <c r="K17" s="23" t="s">
@@ -19827,14 +19834,14 @@
         <v>0</v>
       </c>
       <c r="AV17" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW17" s="31">
         <v>0</v>
       </c>
       <c r="AX17" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY17" s="31"/>
@@ -19846,7 +19853,7 @@
       <c r="BE17" s="35"/>
       <c r="BF17" s="31"/>
       <c r="BG17" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЗПО", note: "Срабатывание ЗПО на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH17" s="37"/>
@@ -19869,11 +19876,11 @@
       </c>
       <c r="H18" s="25"/>
       <c r="I18" s="25">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="J18" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>11</v>
-      </c>
-      <c r="J18" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб. ЗП ВН</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -19950,14 +19957,14 @@
         <v>0</v>
       </c>
       <c r="AV18" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW18" s="31">
         <v>0</v>
       </c>
       <c r="AX18" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY18" s="31"/>
@@ -19969,7 +19976,7 @@
       <c r="BE18" s="35"/>
       <c r="BF18" s="31"/>
       <c r="BG18" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб. ЗП ВН", note: "Срабатывание ЗП ВН", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH18" s="37"/>
@@ -19992,11 +19999,11 @@
       </c>
       <c r="H19" s="25"/>
       <c r="I19" s="25">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="J19" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="J19" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб. ЗП СН(НН1)</v>
       </c>
       <c r="K19" s="23" t="s">
@@ -20073,14 +20080,14 @@
         <v>0</v>
       </c>
       <c r="AV19" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW19" s="31">
         <v>0</v>
       </c>
       <c r="AX19" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY19" s="31"/>
@@ -20092,7 +20099,7 @@
       <c r="BE19" s="35"/>
       <c r="BF19" s="31"/>
       <c r="BG19" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб. ЗП СН(НН1)", note: "Срабатывание ЗП CН (НН1)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH19" s="37"/>
@@ -20115,11 +20122,11 @@
       </c>
       <c r="H20" s="25"/>
       <c r="I20" s="25">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="J20" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="J20" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб. ЗП НН(НН2)</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -20196,14 +20203,14 @@
         <v>0</v>
       </c>
       <c r="AV20" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW20" s="31">
         <v>0</v>
       </c>
       <c r="AX20" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY20" s="31"/>
@@ -20215,7 +20222,7 @@
       <c r="BE20" s="35"/>
       <c r="BF20" s="31"/>
       <c r="BG20" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб. ЗП НН(НН2)", note: "Срабатывание ЗП НН (НН2)", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH20" s="37"/>
@@ -20238,11 +20245,11 @@
       </c>
       <c r="H21" s="25"/>
       <c r="I21" s="25">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="J21" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="J21" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб. ЛО Т</v>
       </c>
       <c r="K21" s="23" t="s">
@@ -20319,14 +20326,14 @@
         <v>0</v>
       </c>
       <c r="AV21" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW21" s="31">
         <v>0</v>
       </c>
       <c r="AX21" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY21" s="31"/>
@@ -20338,7 +20345,7 @@
       <c r="BE21" s="35"/>
       <c r="BF21" s="31"/>
       <c r="BG21" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб. ЛО Т", note: "Срабатывание общей логики отключения трансформатора", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH21" s="37"/>
@@ -20361,11 +20368,11 @@
       </c>
       <c r="H22" s="25"/>
       <c r="I22" s="25">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="J22" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>13</v>
-      </c>
-      <c r="J22" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб. УРОВ ВН</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -20442,14 +20449,14 @@
         <v>0</v>
       </c>
       <c r="AV22" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW22" s="31">
         <v>0</v>
       </c>
       <c r="AX22" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY22" s="31"/>
@@ -20461,7 +20468,7 @@
       <c r="BE22" s="35"/>
       <c r="BF22" s="31"/>
       <c r="BG22" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб. УРОВ ВН", note: "Срабатывание УРОВ ВН", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH22" s="37"/>
@@ -20484,11 +20491,11 @@
       </c>
       <c r="H23" s="25"/>
       <c r="I23" s="25">
+        <f t="shared" si="10"/>
+        <v>19</v>
+      </c>
+      <c r="J23" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>19</v>
-      </c>
-      <c r="J23" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.УРОВвн на себя</v>
       </c>
       <c r="K23" s="23" t="s">
@@ -20565,14 +20572,14 @@
         <v>0</v>
       </c>
       <c r="AV23" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW23" s="31">
         <v>0</v>
       </c>
       <c r="AX23" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY23" s="31"/>
@@ -20584,7 +20591,7 @@
       <c r="BE23" s="35"/>
       <c r="BF23" s="31"/>
       <c r="BG23" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.УРОВвн на себя", note: "Срабатывание УРОВ &lt;&lt;на себя&gt;&gt;", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH23" s="37"/>
@@ -20607,11 +20614,11 @@
       </c>
       <c r="H24" s="25"/>
       <c r="I24" s="25">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="J24" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>7</v>
-      </c>
-      <c r="J24" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ГЗ сигн</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -20688,14 +20695,14 @@
         <v>0</v>
       </c>
       <c r="AV24" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW24" s="31">
         <v>0</v>
       </c>
       <c r="AX24" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY24" s="31"/>
@@ -20707,7 +20714,7 @@
       <c r="BE24" s="35"/>
       <c r="BF24" s="31"/>
       <c r="BG24" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ГЗ сигн", note: "Сигнализация от ГЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH24" s="37"/>
@@ -20730,11 +20737,11 @@
       </c>
       <c r="H25" s="25"/>
       <c r="I25" s="25">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="J25" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>12</v>
-      </c>
-      <c r="J25" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Низ.изол. ГЗ</v>
       </c>
       <c r="K25" s="23" t="s">
@@ -20811,14 +20818,14 @@
         <v>0</v>
       </c>
       <c r="AV25" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW25" s="31">
         <v>0</v>
       </c>
       <c r="AX25" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY25" s="31"/>
@@ -20830,7 +20837,7 @@
       <c r="BE25" s="35"/>
       <c r="BF25" s="31"/>
       <c r="BG25" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Низ.изол. ГЗ", note: "Низкая изоляция ГЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH25" s="37"/>
@@ -20853,11 +20860,11 @@
       </c>
       <c r="H26" s="25"/>
       <c r="I26" s="25">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="J26" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="J26" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ГЗ заблокирована</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -20934,14 +20941,14 @@
         <v>0</v>
       </c>
       <c r="AV26" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW26" s="31">
         <v>0</v>
       </c>
       <c r="AX26" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY26" s="31"/>
@@ -20953,7 +20960,7 @@
       <c r="BE26" s="35"/>
       <c r="BF26" s="31"/>
       <c r="BG26" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ГЗ заблокирована", note: "ГЗ заблокирована", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH26" s="37"/>
@@ -20976,11 +20983,11 @@
       </c>
       <c r="H27" s="25"/>
       <c r="I27" s="25">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="J27" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>7</v>
-      </c>
-      <c r="J27" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ТЗ сигн</v>
       </c>
       <c r="K27" s="23" t="s">
@@ -21057,14 +21064,14 @@
         <v>0</v>
       </c>
       <c r="AV27" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW27" s="31">
         <v>0</v>
       </c>
       <c r="AX27" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY27" s="31"/>
@@ -21076,7 +21083,7 @@
       <c r="BE27" s="35"/>
       <c r="BF27" s="31"/>
       <c r="BG27" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ТЗ сигн", note: "Сигнализация от ТЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH27" s="37"/>
@@ -21099,11 +21106,11 @@
       </c>
       <c r="H28" s="25"/>
       <c r="I28" s="25">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="J28" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>12</v>
-      </c>
-      <c r="J28" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Низ.изол. ТЗ</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -21180,14 +21187,14 @@
         <v>0</v>
       </c>
       <c r="AV28" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW28" s="31">
         <v>0</v>
       </c>
       <c r="AX28" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY28" s="31"/>
@@ -21199,7 +21206,7 @@
       <c r="BE28" s="35"/>
       <c r="BF28" s="31"/>
       <c r="BG28" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Низ.изол. ТЗ", note: "Низкая изоляция ТЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH28" s="37"/>
@@ -21222,11 +21229,11 @@
       </c>
       <c r="H29" s="25"/>
       <c r="I29" s="25">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="J29" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="J29" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ТЗ заблокирована</v>
       </c>
       <c r="K29" s="23" t="s">
@@ -21303,14 +21310,14 @@
         <v>0</v>
       </c>
       <c r="AV29" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW29" s="31">
         <v>0</v>
       </c>
       <c r="AX29" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY29" s="31"/>
@@ -21322,7 +21329,7 @@
       <c r="BE29" s="35"/>
       <c r="BF29" s="31"/>
       <c r="BG29" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ТЗ заблокирована", note: "ТЗ заблокирована", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH29" s="37"/>
@@ -21345,11 +21352,11 @@
       </c>
       <c r="H30" s="25"/>
       <c r="I30" s="25">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="J30" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>7</v>
-      </c>
-      <c r="J30" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ТС сигн</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -21426,14 +21433,14 @@
         <v>0</v>
       </c>
       <c r="AV30" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW30" s="31">
         <v>0</v>
       </c>
       <c r="AX30" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY30" s="31"/>
@@ -21445,7 +21452,7 @@
       <c r="BE30" s="35"/>
       <c r="BF30" s="31"/>
       <c r="BG30" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ТС сигн", note: "Сигнализация от ТС", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH30" s="37"/>
@@ -21468,11 +21475,11 @@
       </c>
       <c r="H31" s="25"/>
       <c r="I31" s="25">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="J31" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>7</v>
-      </c>
-      <c r="J31" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ОТ сигн</v>
       </c>
       <c r="K31" s="23" t="s">
@@ -21549,14 +21556,14 @@
         <v>0</v>
       </c>
       <c r="AV31" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW31" s="31">
         <v>0</v>
       </c>
       <c r="AX31" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY31" s="31"/>
@@ -21568,7 +21575,7 @@
       <c r="BE31" s="35"/>
       <c r="BF31" s="31"/>
       <c r="BG31" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ОТ сигн", note: "Контроль оперативного тока", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH31" s="37"/>
@@ -21591,11 +21598,11 @@
       </c>
       <c r="H32" s="25"/>
       <c r="I32" s="25">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="J32" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="J32" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ОТ НН сигн</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -21672,14 +21679,14 @@
         <v>0</v>
       </c>
       <c r="AV32" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW32" s="31">
         <v>0</v>
       </c>
       <c r="AX32" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY32" s="31"/>
@@ -21691,7 +21698,7 @@
       <c r="BE32" s="35"/>
       <c r="BF32" s="31"/>
       <c r="BG32" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ОТ НН сигн", note: "Контроль оперативного тока НН", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH32" s="37"/>
@@ -21714,11 +21721,11 @@
       </c>
       <c r="H33" s="25"/>
       <c r="I33" s="25">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="J33" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="J33" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Внеш. откл</v>
       </c>
       <c r="K33" s="23" t="s">
@@ -21795,14 +21802,14 @@
         <v>0</v>
       </c>
       <c r="AV33" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW33" s="31">
         <v>0</v>
       </c>
       <c r="AX33" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY33" s="31"/>
@@ -21814,7 +21821,7 @@
       <c r="BE33" s="35"/>
       <c r="BF33" s="31"/>
       <c r="BG33" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Внеш. откл", note: "Внешнее отключение", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH33" s="37"/>
@@ -21837,11 +21844,11 @@
       </c>
       <c r="H34" s="25"/>
       <c r="I34" s="25">
-        <f t="shared" ref="I34:I37" si="15">LEN(F34)</f>
+        <f t="shared" ref="I34:I37" si="14">LEN(F34)</f>
         <v>18</v>
       </c>
       <c r="J34" s="25" t="str">
-        <f t="shared" ref="J34:J37" si="16">IF(LEN(F34)&lt;=$J$1,F34,"")</f>
+        <f t="shared" ref="J34:J37" si="15">IF(LEN(F34)&lt;=$J$1,F34,"")</f>
         <v>Вых.цепи разобраны</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -21918,14 +21925,14 @@
         <v>0</v>
       </c>
       <c r="AV34" s="31">
-        <f t="shared" ref="AV34:AV37" si="17">BIN2DEC(CONCATENATE(0,0,0,0,AR34,AS34,AT34,AU34))</f>
+        <f t="shared" ref="AV34:AV37" si="16">BIN2DEC(CONCATENATE(0,0,0,0,AR34,AS34,AT34,AU34))</f>
         <v>0</v>
       </c>
       <c r="AW34" s="31">
         <v>0</v>
       </c>
       <c r="AX34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY34" s="31"/>
@@ -21937,7 +21944,7 @@
       <c r="BE34" s="35"/>
       <c r="BF34" s="31"/>
       <c r="BG34" s="36" t="str">
-        <f t="shared" ref="BG34:BG37" si="18">CONCATENATE("description: """,F34,"""", ", ", "note: """,E34,"""",", ","group: """, B34, """",", ","minValue: ", S34,", ","maxValue: ", T34,", ","step: ", U34,", ","units: """, R34, """",", ","defaultValue: ", X34,", ","eventRegistration: ", Y34,)</f>
+        <f t="shared" ref="BG34:BG37" si="17">CONCATENATE("description: """,F34,"""", ", ", "note: """,E34,"""",", ","group: """, B34, """",", ","minValue: ", S34,", ","maxValue: ", T34,", ","step: ", U34,", ","units: """, R34, """",", ","defaultValue: ", X34,", ","eventRegistration: ", Y34,)</f>
         <v>description: "Вых.цепи разобраны", note: "Выходные цепи разобраны", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH34" s="37"/>
@@ -21960,11 +21967,11 @@
       </c>
       <c r="H35" s="25"/>
       <c r="I35" s="25">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+      <c r="J35" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>11</v>
-      </c>
-      <c r="J35" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>БИ выведены</v>
       </c>
       <c r="K35" s="23" t="s">
@@ -22041,14 +22048,14 @@
         <v>0</v>
       </c>
       <c r="AV35" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW35" s="31">
         <v>0</v>
       </c>
       <c r="AX35" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY35" s="31"/>
@@ -22060,7 +22067,7 @@
       <c r="BE35" s="35"/>
       <c r="BF35" s="31"/>
       <c r="BG35" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "БИ выведены", note: "БИ выведены", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH35" s="37"/>
@@ -22083,11 +22090,11 @@
       </c>
       <c r="H36" s="25"/>
       <c r="I36" s="25">
+        <f t="shared" si="14"/>
+        <v>19</v>
+      </c>
+      <c r="J36" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>19</v>
-      </c>
-      <c r="J36" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Общ. внеш. сигн. СС</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -22164,14 +22171,14 @@
         <v>0</v>
       </c>
       <c r="AV36" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW36" s="31">
         <v>0</v>
       </c>
       <c r="AX36" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY36" s="31"/>
@@ -22183,7 +22190,7 @@
       <c r="BE36" s="35"/>
       <c r="BF36" s="31"/>
       <c r="BG36" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Общ. внеш. сигн. СС", note: "Общий внешний сигнал от СС", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH36" s="37"/>
@@ -22206,11 +22213,11 @@
       </c>
       <c r="H37" s="25"/>
       <c r="I37" s="25">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="J37" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-      <c r="J37" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>IRF</v>
       </c>
       <c r="K37" s="23" t="s">
@@ -22287,14 +22294,14 @@
         <v>0</v>
       </c>
       <c r="AV37" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW37" s="31">
         <v>0</v>
       </c>
       <c r="AX37" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY37" s="31"/>
@@ -22306,7 +22313,7 @@
       <c r="BE37" s="35"/>
       <c r="BF37" s="31"/>
       <c r="BG37" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "IRF", note: "Неисправность терминала", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH37" s="37"/>
@@ -26147,15 +26154,15 @@
       <c r="AW1" s="11"/>
       <c r="AX1" s="11"/>
       <c r="AY1" s="13"/>
-      <c r="AZ1" s="58" t="s">
+      <c r="AZ1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="BA1" s="59"/>
-      <c r="BB1" s="59"/>
-      <c r="BC1" s="59"/>
-      <c r="BD1" s="59"/>
-      <c r="BE1" s="59"/>
-      <c r="BF1" s="59"/>
+      <c r="BA1" s="60"/>
+      <c r="BB1" s="60"/>
+      <c r="BC1" s="60"/>
+      <c r="BD1" s="60"/>
+      <c r="BE1" s="60"/>
+      <c r="BF1" s="60"/>
     </row>
     <row r="2" spans="1:16379" s="22" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -43003,15 +43010,15 @@
       <c r="AX1" s="11"/>
       <c r="AY1" s="11"/>
       <c r="AZ1" s="13"/>
-      <c r="BA1" s="58" t="s">
+      <c r="BA1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="BB1" s="59"/>
-      <c r="BC1" s="59"/>
-      <c r="BD1" s="59"/>
-      <c r="BE1" s="59"/>
-      <c r="BF1" s="59"/>
-      <c r="BG1" s="59"/>
+      <c r="BB1" s="60"/>
+      <c r="BC1" s="60"/>
+      <c r="BD1" s="60"/>
+      <c r="BE1" s="60"/>
+      <c r="BF1" s="60"/>
+      <c r="BG1" s="60"/>
     </row>
     <row r="2" spans="1:16380" s="22" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -43035,7 +43042,7 @@
       <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="58" t="s">
         <v>241</v>
       </c>
       <c r="I2" s="14" t="s">
